--- a/data/trans_camb/P36BPD07_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P36BPD07_R-Habitat-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-14,95</t>
+          <t>-14,59</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-9,03</t>
+          <t>-9,57</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-11,89</t>
+          <t>-12,01</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,48; -10,29</t>
+          <t>-18,73; -10,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,39; -5,5</t>
+          <t>-13,33; -6,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,5; -8,92</t>
+          <t>-14,73; -9,14</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-16,69%</t>
+          <t>-16,3%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-10,07%</t>
+          <t>-10,67%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-13,27%</t>
+          <t>-13,4%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,55; -11,76</t>
+          <t>-20,7; -11,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,59; -6,22</t>
+          <t>-14,57; -6,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,03; -10,17</t>
+          <t>-16,21; -10,28</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-8,79</t>
+          <t>-15,59</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-13,96</t>
+          <t>-14,69</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-11,33</t>
+          <t>-15,14</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 5,1</t>
+          <t>-19,78; -11,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,16; -10,41</t>
+          <t>-18,09; -11,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,55; -2,55</t>
+          <t>-17,72; -12,62</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-10,61%</t>
+          <t>-18,83%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-16,1%</t>
+          <t>-16,94%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-13,36%</t>
+          <t>-17,85%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 6,14</t>
+          <t>-23,5; -14,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,58; -12,3</t>
+          <t>-20,45; -13,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,26; -3,02</t>
+          <t>-20,7; -15,04</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-6,63</t>
+          <t>-6,59</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>-4,11</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,99</t>
+          <t>-5,34</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,28; -1,87</t>
+          <t>-10,99; -1,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 10,98</t>
+          <t>-7,81; -0,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 5,3</t>
+          <t>-8,3; -2,39</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-8,03%</t>
+          <t>-7,98%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>-4,97%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-2,41%</t>
+          <t>-6,46%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,57; -2,31</t>
+          <t>-13,19; -2,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 13,62</t>
+          <t>-9,34; -0,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 6,57</t>
+          <t>-9,92; -2,99</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-12,27</t>
+          <t>-14,0</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-9,05</t>
+          <t>-11,64</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-10,48</t>
+          <t>-12,74</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,56; -8,21</t>
+          <t>-17,8; -9,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,41; -4,64</t>
+          <t>-14,86; -8,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,3; -7,27</t>
+          <t>-15,18; -9,73</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-14,62%</t>
+          <t>-16,68%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-10,31%</t>
+          <t>-13,26%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-12,19%</t>
+          <t>-14,82%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,37; -10,05</t>
+          <t>-20,84; -12,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,95; -5,33</t>
+          <t>-16,73; -9,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,31; -8,54</t>
+          <t>-17,47; -11,52</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-10,52</t>
+          <t>-12,92</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-7,79</t>
+          <t>-10,43</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-9,11</t>
+          <t>-11,64</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,29; -4,2</t>
+          <t>-14,96; -10,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -4,09</t>
+          <t>-12,25; -8,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,06; -5,98</t>
+          <t>-12,87; -10,23</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-12,46%</t>
+          <t>-15,31%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-8,98%</t>
+          <t>-12,03%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-10,64%</t>
+          <t>-13,6%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,66; -4,98</t>
+          <t>-17,6; -12,91</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,64; -4,74</t>
+          <t>-14,01; -10,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,85; -7,0</t>
+          <t>-15,01; -12,05</t>
         </is>
       </c>
     </row>
